--- a/g4_rtos/docs/APK5_Requirements_ASPICE.xlsx
+++ b/g4_rtos/docs/APK5_Requirements_ASPICE.xlsx
@@ -4804,12 +4804,24 @@
       </c>
       <c r="H5" s="16" t="inlineStr">
         <is>
-          <t>Not run</t>
-        </is>
-      </c>
-      <c r="I5" s="19" t="inlineStr"/>
-      <c r="J5" s="19" t="inlineStr"/>
-      <c r="K5" s="19" t="inlineStr"/>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="I5" s="19" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="J5" s="19" t="inlineStr">
+        <is>
+          <t>M. Hanzouti</t>
+        </is>
+      </c>
+      <c r="K5" s="19" t="inlineStr">
+        <is>
+          <t>Automated run</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="17" t="inlineStr">
@@ -4849,12 +4861,24 @@
       </c>
       <c r="H6" s="16" t="inlineStr">
         <is>
-          <t>Not run</t>
-        </is>
-      </c>
-      <c r="I6" s="19" t="inlineStr"/>
-      <c r="J6" s="19" t="inlineStr"/>
-      <c r="K6" s="19" t="inlineStr"/>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="I6" s="19" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="J6" s="19" t="inlineStr">
+        <is>
+          <t>M. Hanzouti</t>
+        </is>
+      </c>
+      <c r="K6" s="19" t="inlineStr">
+        <is>
+          <t>Automated run</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="14" t="inlineStr">
@@ -4894,12 +4918,24 @@
       </c>
       <c r="H7" s="16" t="inlineStr">
         <is>
-          <t>Not run</t>
-        </is>
-      </c>
-      <c r="I7" s="19" t="inlineStr"/>
-      <c r="J7" s="19" t="inlineStr"/>
-      <c r="K7" s="19" t="inlineStr"/>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="I7" s="19" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="J7" s="19" t="inlineStr">
+        <is>
+          <t>M. Hanzouti</t>
+        </is>
+      </c>
+      <c r="K7" s="19" t="inlineStr">
+        <is>
+          <t>Automated run</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="17" t="inlineStr">
@@ -4939,12 +4975,24 @@
       </c>
       <c r="H8" s="16" t="inlineStr">
         <is>
-          <t>Not run</t>
-        </is>
-      </c>
-      <c r="I8" s="19" t="inlineStr"/>
-      <c r="J8" s="19" t="inlineStr"/>
-      <c r="K8" s="19" t="inlineStr"/>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="I8" s="19" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="J8" s="19" t="inlineStr">
+        <is>
+          <t>M. Hanzouti</t>
+        </is>
+      </c>
+      <c r="K8" s="19" t="inlineStr">
+        <is>
+          <t>Automated run</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
@@ -4984,12 +5032,24 @@
       </c>
       <c r="H9" s="16" t="inlineStr">
         <is>
-          <t>Not run</t>
-        </is>
-      </c>
-      <c r="I9" s="19" t="inlineStr"/>
-      <c r="J9" s="19" t="inlineStr"/>
-      <c r="K9" s="19" t="inlineStr"/>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="I9" s="19" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="J9" s="19" t="inlineStr">
+        <is>
+          <t>M. Hanzouti</t>
+        </is>
+      </c>
+      <c r="K9" s="19" t="inlineStr">
+        <is>
+          <t>Automated run</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="17" t="inlineStr">
@@ -5029,12 +5089,24 @@
       </c>
       <c r="H10" s="16" t="inlineStr">
         <is>
-          <t>Not run</t>
-        </is>
-      </c>
-      <c r="I10" s="19" t="inlineStr"/>
-      <c r="J10" s="19" t="inlineStr"/>
-      <c r="K10" s="19" t="inlineStr"/>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="I10" s="19" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="J10" s="19" t="inlineStr">
+        <is>
+          <t>M. Hanzouti</t>
+        </is>
+      </c>
+      <c r="K10" s="19" t="inlineStr">
+        <is>
+          <t>Automated run</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="14" t="inlineStr">
@@ -5074,12 +5146,24 @@
       </c>
       <c r="H11" s="16" t="inlineStr">
         <is>
-          <t>Not run</t>
-        </is>
-      </c>
-      <c r="I11" s="19" t="inlineStr"/>
-      <c r="J11" s="19" t="inlineStr"/>
-      <c r="K11" s="19" t="inlineStr"/>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="I11" s="19" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="J11" s="19" t="inlineStr">
+        <is>
+          <t>M. Hanzouti</t>
+        </is>
+      </c>
+      <c r="K11" s="19" t="inlineStr">
+        <is>
+          <t>Automated run</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="17" t="inlineStr">
@@ -5119,12 +5203,24 @@
       </c>
       <c r="H12" s="16" t="inlineStr">
         <is>
-          <t>Not run</t>
-        </is>
-      </c>
-      <c r="I12" s="19" t="inlineStr"/>
-      <c r="J12" s="19" t="inlineStr"/>
-      <c r="K12" s="19" t="inlineStr"/>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="I12" s="19" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="J12" s="19" t="inlineStr">
+        <is>
+          <t>M. Hanzouti</t>
+        </is>
+      </c>
+      <c r="K12" s="19" t="inlineStr">
+        <is>
+          <t>Automated run</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="14" t="inlineStr">
@@ -5164,12 +5260,24 @@
       </c>
       <c r="H13" s="16" t="inlineStr">
         <is>
-          <t>Not run</t>
-        </is>
-      </c>
-      <c r="I13" s="19" t="inlineStr"/>
-      <c r="J13" s="19" t="inlineStr"/>
-      <c r="K13" s="19" t="inlineStr"/>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="I13" s="19" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="J13" s="19" t="inlineStr">
+        <is>
+          <t>M. Hanzouti</t>
+        </is>
+      </c>
+      <c r="K13" s="19" t="inlineStr">
+        <is>
+          <t>Automated run</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="17" t="inlineStr">
@@ -5254,12 +5362,24 @@
       </c>
       <c r="H15" s="16" t="inlineStr">
         <is>
-          <t>Not run</t>
-        </is>
-      </c>
-      <c r="I15" s="19" t="inlineStr"/>
-      <c r="J15" s="19" t="inlineStr"/>
-      <c r="K15" s="19" t="inlineStr"/>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="I15" s="19" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="J15" s="19" t="inlineStr">
+        <is>
+          <t>M. Hanzouti</t>
+        </is>
+      </c>
+      <c r="K15" s="19" t="inlineStr">
+        <is>
+          <t>Automated run</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="17" t="inlineStr">
@@ -5344,12 +5464,24 @@
       </c>
       <c r="H17" s="16" t="inlineStr">
         <is>
-          <t>Not run</t>
-        </is>
-      </c>
-      <c r="I17" s="19" t="inlineStr"/>
-      <c r="J17" s="19" t="inlineStr"/>
-      <c r="K17" s="19" t="inlineStr"/>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="I17" s="19" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="J17" s="19" t="inlineStr">
+        <is>
+          <t>M. Hanzouti</t>
+        </is>
+      </c>
+      <c r="K17" s="19" t="inlineStr">
+        <is>
+          <t>Automated run</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="17" t="inlineStr">
